--- a/Data/Define.xlsx
+++ b/Data/Define.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3089636D-F918-475E-8095-9A9550A41180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3E084B-E44A-4511-8FE6-CD9463936DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43260" yWindow="1740" windowWidth="31155" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,6 +43,10 @@
   </si>
   <si>
     <t>StarforceRestoration2_Price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponAwakeAddLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -390,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -437,6 +441,14 @@
         <v>1000000</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/Define.xlsx
+++ b/Data/Define.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3E084B-E44A-4511-8FE6-CD9463936DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D777FB-29E8-4F24-BA57-829DECAA6FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43260" yWindow="1740" windowWidth="31155" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="2790" windowWidth="31155" windowHeight="16815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,6 +47,14 @@
   </si>
   <si>
     <t>WeaponAwakeAddLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponCombineCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponBaseMaxLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -394,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -449,6 +457,22 @@
         <v>20</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/Define.xlsx
+++ b/Data/Define.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D777FB-29E8-4F24-BA57-829DECAA6FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FE3E0D-1B85-4B47-A67D-152C0B6E97C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="2790" windowWidth="31155" windowHeight="16815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39915" yWindow="3630" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,6 +55,10 @@
   </si>
   <si>
     <t>WeaponBaseMaxLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponLevelUpCostKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,7 +66,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +80,11 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,8 +107,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -402,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -473,6 +485,14 @@
         <v>100</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>1003</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/Define.xlsx
+++ b/Data/Define.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FE3E0D-1B85-4B47-A67D-152C0B6E97C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7A40E1-092C-43CC-AE61-CC87650D3A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39915" yWindow="3630" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15975" yWindow="2685" windowWidth="19860" windowHeight="16035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,6 +59,18 @@
   </si>
   <si>
     <t>WeaponLevelUpCostKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LanternBaseMaxLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LanternCombineCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SummonAdDrawCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -66,7 +78,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,11 +92,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,11 +114,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -414,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -486,11 +490,35 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <v>1003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
